--- a/Shared/XLS/Npc.xlsx
+++ b/Shared/XLS/Npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>!Table</t>
   </si>
@@ -368,6 +368,22 @@
   </si>
   <si>
     <t>Portrait</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Storage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portal</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -915,7 +931,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1136,7 +1152,7 @@
         <v>57</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -1160,7 +1176,7 @@
         <v>54</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F5" s="11"/>
       <c r="H5" s="11"/>
@@ -1184,7 +1200,7 @@
         <v>55</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -1207,7 +1223,7 @@
         <v>56</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
